--- a/public/sap-reporting/expansion-150-downloads/EXT-PP12-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-PP12-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rfa2faec153a040d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Red16d801a64b4f71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rd3f61dbcebca46d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rb03d394c62aa4282"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R7f9fa207c363446d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R189da9127e6f43e0"/>
   </x:sheets>
 </x:workbook>
 </file>
